--- a/stories/arbres/ATOM-EMO.LEX.004-03.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.004-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Kenzo est au jardin avec maman. Un ballon rouge arrive vite. Kenzo sursaute. Il est surpris. Ses épaules montent. Maman dit : tu es surpris. On respire. On comprend avant d'agir. Kenzo souffle. Il regarde. Le ballon est un ballon. Rien d'autre. Kenzo comprend. Il le ramène, tout doux. Maman dit : surpris, respirer, comprendre.</t>
+          <t>Kenzo est au jardin avec maman. Un ballon rouge arrive vite. Kenzo sursaute. Il est surpris. Ses épaules montent. Tu es surpris. On respire. On comprend avant d'agir. Kenzo souffle. Il regarde. Le ballon est un ballon. Rien d'autre. Kenzo comprend. Il le ramène, tout doux. Surpris, respirer, comprendre.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,14 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo est au jardin avec maman. Un ballon rouge arrive vite. Kenzo sursaute. Il est surpris. Ses épaules montent.
+maman|Tu es surpris. On respire. On comprend avant d'agir.
+narrateur|Kenzo souffle. Il regarde. Le ballon est un ballon. Rien d'autre. Kenzo comprend. Il le ramène, tout doux.
+maman|Surpris, respirer, comprendre.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1489,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Le ballon arrive vite. Quelle émotion ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1662,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo a été surpris. Il a soufflé. Il a compris.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1825,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maman pose le ballon. Kenzo boit une gorgée.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1992,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2032,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.004-03.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.004-03.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1313,6 +1318,7 @@
 maman|Surpris, respirer, comprendre.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1496,6 +1502,7 @@
           <t>narrateur|Le ballon arrive vite. Quelle émotion ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1667,6 +1674,7 @@
           <t>narrateur|Kenzo a été surpris. Il a soufflé. Il a compris.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1830,6 +1838,7 @@
           <t>narrateur|Maman pose le ballon. Kenzo boit une gorgée.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1997,6 +2006,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2015,7 +2025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2039,6 +2049,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2240,6 +2264,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-EMO.LEX.004-03.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.004-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kenzo est surpris par le ballon</t>
+          <t>Le ballon d'Aniss</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Un ballon rouge arrive vite. Aniss est surpris. Il souffle. Il regarde. Il comprend. Il le ramène tout doux.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Kenzo est au jardin avec maman. Un ballon rouge arrive vite. Kenzo sursaute. Il est surpris. Ses épaules montent. Tu es surpris. On respire. On comprend avant d'agir. Kenzo souffle. Il regarde. Le ballon est un ballon. Rien d'autre. Kenzo comprend. Il le ramène, tout doux. Surpris, respirer, comprendre.</t>
+          <t>Une pince à linge tombe dans l'herbe. Elle est bleue, un peu chaude. Le thym du jardin sent le soleil. Un arrosoir vert attend près des fleurs. L'eau y fait un petit miroir. L'herbe chatouille les chevilles. Elle est encore un peu humide. Une abeille se pose sur une fleur. La fleur est jaune et ouverte. Un rire arrive de plus loin. Puis le rire s'arrête. Tu as vu l'abeille, Aniss ? Elle est sur le jaune. Elle reste sur la fleur. On la laisse. Tu ramasses la pince ? Oui, maman. Aniss pose la pince sur l'arrosoir. En ce moment, Aniss marche dans l'herbe. Ses pieds sont nus et tièdes. Un ballon rouge arrive vite. Il rebondit près des orteils. Aniss sursaute. Ses épaules montent. Je suis surpris. Tu es surpris. Ce n'est pas honteux. On respire. On comprend avant d'agir. Aniss souffle une grande fois. Ses épaules redescendent. Tu veux regarder ? Oui. Il regarde le ballon. Le ballon est un ballon. Rien d'autre. C'est un ballon. Oui. Tu as compris. Aniss le ramène, tout doux. Le caoutchouc est chaud de soleil. Bravo, Aniss. Tu as d'abord respiré. Puis tu as regardé. Tu as fait du bon travail. Surpris. Respirer. Comprendre. Oui. Surpris, respirer, comprendre. Le linge claque plus loin, plus doux. L'abeille est partie de la fleur. Il est rouge. Oui. On le pose ici. Le ballon s'arrête près de l'arrosoir. L'herbe redevient calme. Tu veux une gorgée ? Oui. L'eau de la tasse est fraîche. Le thym sent encore.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,10 +1324,67 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo est au jardin avec maman. Un ballon rouge arrive vite. Kenzo sursaute. Il est surpris. Ses épaules montent.
-maman|Tu es surpris. On respire. On comprend avant d'agir.
-narrateur|Kenzo souffle. Il regarde. Le ballon est un ballon. Rien d'autre. Kenzo comprend. Il le ramène, tout doux.
-maman|Surpris, respirer, comprendre.</t>
+          <t>narrateur|Une pince à linge tombe dans l'herbe.
+narrateur|Elle est bleue, un peu chaude.
+narrateur|Le thym du jardin sent le soleil.
+narrateur|Un arrosoir vert attend près des fleurs.
+narrateur|L'eau y fait un petit miroir.
+narrateur|L'herbe chatouille les chevilles.
+narrateur|Elle est encore un peu humide.
+narrateur|Une abeille se pose sur une fleur.
+narrateur|La fleur est jaune et ouverte.
+narrateur|Un rire arrive de plus loin.
+narrateur|Puis le rire s'arrête.
+maman|Tu as vu l'abeille, Aniss ?
+enfant-m|Elle est sur le jaune.
+maman|Elle reste sur la fleur.
+maman|On la laisse.
+maman|Tu ramasses la pince ?
+enfant-m|Oui, maman.
+narrateur|Aniss pose la pince sur l'arrosoir.
+narrateur|En ce moment, Aniss marche dans l'herbe.
+narrateur|Ses pieds sont nus et tièdes.
+narrateur|Un ballon rouge arrive vite.
+narrateur|Il rebondit près des orteils.
+narrateur|Aniss sursaute.
+narrateur|Ses épaules montent.
+enfant-m|Je suis surpris.
+maman|Tu es surpris.
+maman|Ce n'est pas honteux.
+maman|On respire.
+maman|On comprend avant d'agir.
+narrateur|Aniss souffle une grande fois.
+narrateur|Ses épaules redescendent.
+maman|Tu veux regarder ?
+enfant-m|Oui.
+narrateur|Il regarde le ballon.
+narrateur|Le ballon est un ballon.
+narrateur|Rien d'autre.
+enfant-m|C'est un ballon.
+maman|Oui.
+maman|Tu as compris.
+narrateur|Aniss le ramène, tout doux.
+narrateur|Le caoutchouc est chaud de soleil.
+maman|Bravo, Aniss.
+maman|Tu as d'abord respiré.
+maman|Puis tu as regardé.
+maman|Tu as fait du bon travail.
+enfant-m|Surpris.
+enfant-m|Respirer.
+enfant-m|Comprendre.
+maman|Oui.
+maman|Surpris, respirer, comprendre.
+narrateur|Le linge claque plus loin, plus doux.
+narrateur|L'abeille est partie de la fleur.
+enfant-m|Il est rouge.
+maman|Oui.
+maman|On le pose ici.
+narrateur|Le ballon s'arrête près de l'arrosoir.
+narrateur|L'herbe redevient calme.
+maman|Tu veux une gorgée ?
+enfant-m|Oui.
+narrateur|L'eau de la tasse est fraîche.
+narrateur|Le thym sent encore.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1499,7 +1568,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Le ballon arrive vite. Quelle émotion ?</t>
+          <t>narrateur|Le ballon arrive vite.
+narrateur|Quelle émotion ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1527,7 +1597,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Kenzo a été surpris. Il a soufflé. Il a compris.</t>
+          <t>Aniss touche encore le ballon. J'ai été surpris. Oui. Tu as soufflé. Tu as compris. Avant d'agir. Bravo, Aniss. Tu as fait du bon travail. D'abord respirer. Oui. Le rouge brille encore dans l'herbe.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1671,7 +1741,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo a été surpris. Il a soufflé. Il a compris.</t>
+          <t>narrateur|Aniss touche encore le ballon.
+enfant-m|J'ai été surpris.
+maman|Oui.
+maman|Tu as soufflé.
+maman|Tu as compris.
+maman|Avant d'agir.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+enfant-m|D'abord respirer.
+maman|Oui.
+narrateur|Le rouge brille encore dans l'herbe.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1699,7 +1779,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman pose le ballon. Kenzo boit une gorgée.</t>
+          <t>Maman pose le ballon. Aniss boit une gorgée. On reste dans l'herbe un peu ? Oui, maman. Tu as nommé : surpris. Tu as respiré. Tu as regardé. L'eau est fraîche dans la tasse. La serviette blanche ne claque plus. C'était un ballon. Oui. Tu as compris.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1835,7 +1915,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman pose le ballon. Kenzo boit une gorgée.</t>
+          <t>narrateur|Maman pose le ballon.
+narrateur|Aniss boit une gorgée.
+maman|On reste dans l'herbe un peu ?
+enfant-m|Oui, maman.
+maman|Tu as nommé : surpris.
+maman|Tu as respiré.
+maman|Tu as regardé.
+narrateur|L'eau est fraîche dans la tasse.
+narrateur|La serviette blanche ne claque plus.
+enfant-m|C'était un ballon.
+maman|Oui.
+maman|Tu as compris.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1863,7 +1954,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai dit : je suis surpris. J'ai soufflé. J'ai compris. Bravo, Aniss. Tu as fait du bon travail. Le ballon reste dans l'herbe. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2003,7 +2094,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai dit : je suis surpris.
+enfant-m|J'ai soufflé.
+enfant-m|J'ai compris.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+narrateur|Le ballon reste dans l'herbe.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2025,7 +2122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2063,6 +2160,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.004-03.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.004-03.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une pince à linge tombe dans l'herbe. Elle est bleue, un peu chaude. Le thym du jardin sent le soleil. Un arrosoir vert attend près des fleurs. L'eau y fait un petit miroir. L'herbe chatouille les chevilles. Elle est encore un peu humide. Une abeille se pose sur une fleur. La fleur est jaune et ouverte. Un rire arrive de plus loin. Puis le rire s'arrête. Tu as vu l'abeille, Aniss ? Elle est sur le jaune. Elle reste sur la fleur. On la laisse. Tu ramasses la pince ? Oui, maman. Aniss pose la pince sur l'arrosoir. En ce moment, Aniss marche dans l'herbe. Ses pieds sont nus et tièdes. Un ballon rouge arrive vite. Il rebondit près des orteils. Aniss sursaute. Ses épaules montent. Je suis surpris. Tu es surpris. Ce n'est pas honteux. On respire. On comprend avant d'agir. Aniss souffle une grande fois. Ses épaules redescendent. Tu veux regarder ? Oui. Il regarde le ballon. Le ballon est un ballon. Rien d'autre. C'est un ballon. Oui. Tu as compris. Aniss le ramène, tout doux. Le caoutchouc est chaud de soleil. Bravo, Aniss. Tu as d'abord respiré. Puis tu as regardé. Tu as fait du bon travail. Surpris. Respirer. Comprendre. Oui. Surpris, respirer, comprendre. Le linge claque plus loin, plus doux. L'abeille est partie de la fleur. Il est rouge. Oui. On le pose ici. Le ballon s'arrête près de l'arrosoir. L'herbe redevient calme. Tu veux une gorgée ? Oui. L'eau de la tasse est fraîche. Le thym sent encore.</t>
+          <t>Une pince à linge tombe dans l'herbe. Elle est bleue, un peu chaude. Le thym du jardin sent le soleil. Un arrosoir vert attend près des fleurs. L'eau y fait un petit miroir. L'herbe chatouille les chevilles. Elle est encore un peu humide. Une abeille se pose sur une fleur. La fleur est jaune et ouverte. Un rire arrive de plus loin. Puis le rire s'arrête. Tu as vu l'abeille, Aniss ? Elle est sur le jaune. Elle reste sur la fleur. On la laisse. Tu ramasses la pince ? Oui, maman. Aniss pose la pince sur l'arrosoir. En ce moment, Aniss marche dans l'herbe. Ses pieds sont nus et tièdes. Un ballon rouge arrive vite. Il rebondit près des orteils. Aniss sursaute. Ses épaules montent. Je suis surpris. Tu es surpris. Ce n'est pas honteux. On respire. On comprend avant d'agir. Aniss souffle une grande fois. Ses épaules redescendent. Tu veux regarder ? Oui. Il regarde le ballon. Le ballon est un ballon. Rien d'autre. C'est un ballon. Oui. Tu as compris. Aniss le ramène, tout doux. Le caoutchouc est chaud de soleil. Bravo, Aniss. Tu as d'abord respiré. Puis tu as regardé. Surpris. Respirer. Comprendre. Oui. Surpris, respirer, comprendre. Le linge claque plus loin, plus doux. L'abeille est partie de la fleur. Il est rouge. Oui. On le pose ici. Le ballon s'arrête près de l'arrosoir. L'herbe redevient calme. Tu veux une gorgée ? Oui. L'eau de la tasse est fraîche. Le thym sent encore.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Kenzo est au jardin avec maman. Un ballon rouge arrive vite. Kenzo sursaute. Il est &lt;emphasis level="moderate"&gt;surpris&lt;/emphasis&gt;. Ses épaules montent. Maman dit : tu es surpris. On respire. On comprend avant d'agir. Kenzo souffle. Il regarde. Le ballon est un ballon. Rien d'autre. Kenzo comprend. Il le ramène, tout doux. Maman dit : surpris, respirer, comprendre.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une pince à linge tombe dans l'herbe. Elle est bleue, un peu chaude. Le thym du jardin sent le soleil. Un arrosoir vert attend près des fleurs. L'eau y fait un petit miroir. L'herbe chatouille les chevilles. Elle est encore un peu humide. Une abeille se pose sur une fleur. La fleur est jaune et ouverte. Un rire arrive de plus loin. Puis le rire s'arrête. Tu as vu l'abeille, Aniss ? Elle est sur le jaune. Elle reste sur la fleur. On la laisse. Tu ramasses la pince ? Oui, maman. Aniss pose la pince sur l'arrosoir. En ce moment, Aniss marche dans l'herbe. Ses pieds sont nus et tièdes. Un ballon rouge arrive vite. Il rebondit près des orteils. Aniss sursaute. Ses épaules montent. Je suis surpris. Tu es surpris. Ce n'est pas honteux. On respire. On comprend avant d'agir. Aniss souffle une grande fois. Ses épaules redescendent. Tu veux regarder ? Oui. Il regarde le ballon. Le ballon est un ballon. Rien d'autre. C'est un ballon. Oui. Tu as compris. Aniss le ramène, tout doux. Le caoutchouc est chaud de soleil. Bravo, Aniss. Tu as d'abord respiré. Puis tu as regardé. Surpris. Respirer. Comprendre. Oui. Surpris, respirer, comprendre. Le linge claque plus loin, plus doux. L'abeille est partie de la fleur. Il est rouge. Oui. On le pose ici. Le ballon s'arrête près de l'arrosoir. L'herbe redevient calme. Tu veux une gorgée ? Oui. L'eau de la tasse est fraîche. Le thym sent encore.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1368,7 +1368,6 @@
 maman|Bravo, Aniss.
 maman|Tu as d'abord respiré.
 maman|Puis tu as regardé.
-maman|Tu as fait du bon travail.
 enfant-m|Surpris.
 enfant-m|Respirer.
 enfant-m|Comprendre.
@@ -1387,7 +1386,6 @@
 narrateur|Le thym sent encore.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1417,7 +1415,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Le ballon arrive vite. Quelle émotion ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le ballon arrive vite. Quelle émotion ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1572,7 +1570,6 @@
 narrateur|Quelle émotion ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1597,12 +1594,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Aniss touche encore le ballon. J'ai été surpris. Oui. Tu as soufflé. Tu as compris. Avant d'agir. Bravo, Aniss. Tu as fait du bon travail. D'abord respirer. Oui. Le rouge brille encore dans l'herbe.</t>
+          <t>Aniss touche encore le ballon. J'ai été surpris. Oui. Tu as soufflé. Tu as compris. Avant d'agir. Bravo, Aniss. D'abord respirer. Oui. Le rouge brille encore dans l'herbe.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Kenzo a été &lt;emphasis level="moderate"&gt;surpris&lt;/emphasis&gt;. Il a soufflé. Il a compris.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss touche encore le ballon. J'ai été surpris. Oui. Tu as soufflé. Tu as compris. Avant d'agir. Bravo, Aniss. D'abord respirer. Oui. Le rouge brille encore dans l'herbe.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1748,13 +1745,11 @@
 maman|Tu as compris.
 maman|Avant d'agir.
 maman|Bravo, Aniss.
-maman|Tu as fait du bon travail.
 enfant-m|D'abord respirer.
 maman|Oui.
 narrateur|Le rouge brille encore dans l'herbe.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1784,7 +1779,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maman pose le ballon. Kenzo boit une gorgée.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman pose le ballon. Aniss boit une gorgée. On reste dans l'herbe un peu ? Oui, maman. Tu as nommé : surpris. Tu as respiré. Tu as regardé. L'eau est fraîche dans la tasse. La serviette blanche ne claque plus. C'était un ballon. Oui. Tu as compris.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1929,7 +1924,6 @@
 maman|Tu as compris.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1954,12 +1948,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai dit : je suis surpris. J'ai soufflé. J'ai compris. Bravo, Aniss. Tu as fait du bon travail. Le ballon reste dans l'herbe. L'histoire est finie.</t>
+          <t>J'ai dit : je suis surpris. J'ai soufflé. J'ai compris. Bravo, Aniss. Le ballon reste dans l'herbe.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai dit : je suis surpris. J'ai soufflé. J'ai compris. Bravo, Aniss. Le ballon reste dans l'herbe.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2098,12 +2092,9 @@
 enfant-m|J'ai soufflé.
 enfant-m|J'ai compris.
 maman|Bravo, Aniss.
-maman|Tu as fait du bon travail.
-narrateur|Le ballon reste dans l'herbe.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le ballon reste dans l'herbe.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2122,7 +2113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2167,6 +2158,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.004-03.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.004-03.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Kenzo, maman</t>
+          <t>Aniss, maman</t>
         </is>
       </c>
     </row>
